--- a/buildplan_generator/output/25-088 GENERATED BUILD PLAN.xlsx
+++ b/buildplan_generator/output/25-088 GENERATED BUILD PLAN.xlsx
@@ -74,14 +74,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FCE4EC"/>
-        <bgColor rgb="00FCE4EC"/>
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
+        <fgColor rgb="00FCE4EC"/>
+        <bgColor rgb="00FCE4EC"/>
       </patternFill>
     </fill>
     <fill>
@@ -543,7 +543,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>25-034, 23-034, 25-002, 23-035, 25-036</t>
+          <t>24-006, 25-087, 25-042, 23-034, 24-041</t>
         </is>
       </c>
     </row>
@@ -635,17 +635,15 @@
         </is>
       </c>
       <c r="E6" s="8" t="n"/>
-      <c r="F6" s="9" t="n">
-        <v>1</v>
-      </c>
+      <c r="F6" s="8" t="n"/>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>global:1.0-1.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I6" s="8" t="n"/>
@@ -673,12 +671,12 @@
       <c r="F7" s="8" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H7" s="8" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I7" s="8" t="n"/>
@@ -722,7 +720,7 @@
       <c r="E9" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F9" s="10" t="n">
+      <c r="F9" s="9" t="n">
         <v>2</v>
       </c>
       <c r="G9" s="8" t="inlineStr">
@@ -732,7 +730,7 @@
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>1.0-3.5</t>
+          <t>ratio=1.00 (0.67-1.50)</t>
         </is>
       </c>
       <c r="I9" s="8" t="n"/>
@@ -759,8 +757,8 @@
       <c r="E10" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="F10" s="10" t="n">
-        <v>9</v>
+      <c r="F10" s="9" t="n">
+        <v>4.3</v>
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
@@ -769,7 +767,7 @@
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>2.0-14.0</t>
+          <t>ratio=1.44 (1.00-2.00)</t>
         </is>
       </c>
       <c r="I10" s="8" t="n"/>
@@ -813,8 +811,8 @@
       <c r="E12" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F12" s="10" t="n">
-        <v>6.5</v>
+      <c r="F12" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
@@ -823,7 +821,7 @@
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>2.0-10.5</t>
+          <t>ratio=1.00 (0.29-2.64)</t>
         </is>
       </c>
       <c r="I12" s="8" t="n"/>
@@ -850,8 +848,8 @@
       <c r="E13" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F13" s="10" t="n">
-        <v>2.5</v>
+      <c r="F13" s="9" t="n">
+        <v>0.5</v>
       </c>
       <c r="G13" s="8" t="inlineStr">
         <is>
@@ -860,7 +858,7 @@
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>2.0-6.5</t>
+          <t>ratio=0.50 (0.20-1.33)</t>
         </is>
       </c>
       <c r="I13" s="8" t="n"/>
@@ -904,8 +902,8 @@
       <c r="E15" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="F15" s="10" t="n">
-        <v>3</v>
+      <c r="F15" s="9" t="n">
+        <v>4.2</v>
       </c>
       <c r="G15" s="8" t="inlineStr">
         <is>
@@ -914,7 +912,7 @@
       </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
-          <t>2.0-4.0</t>
+          <t>ratio=0.83 (0.50-1.12)</t>
         </is>
       </c>
       <c r="I15" s="8" t="n"/>
@@ -958,7 +956,7 @@
       <c r="E17" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F17" s="10" t="n">
+      <c r="F17" s="9" t="n">
         <v>1</v>
       </c>
       <c r="G17" s="8" t="inlineStr">
@@ -968,7 +966,7 @@
       </c>
       <c r="H17" s="8" t="inlineStr">
         <is>
-          <t>1.0-1.0</t>
+          <t>ratio=1.00 (1.00-1.00)</t>
         </is>
       </c>
       <c r="I17" s="8" t="n"/>
@@ -1010,17 +1008,15 @@
         </is>
       </c>
       <c r="E19" s="8" t="n"/>
-      <c r="F19" s="9" t="n">
-        <v>1</v>
-      </c>
+      <c r="F19" s="8" t="n"/>
       <c r="G19" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H19" s="8" t="inlineStr">
         <is>
-          <t>global:1.0-2.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I19" s="8" t="n"/>
@@ -1047,17 +1043,17 @@
       <c r="E20" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F20" s="11" t="n">
-        <v>1.2</v>
+      <c r="F20" s="9" t="n">
+        <v>3</v>
       </c>
       <c r="G20" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H20" s="8" t="inlineStr">
         <is>
-          <t>1.0-1.5</t>
+          <t>ratio=1.50 (1.00-3.00)</t>
         </is>
       </c>
       <c r="I20" s="8" t="n"/>
@@ -1084,8 +1080,8 @@
       <c r="E21" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F21" s="9" t="n">
-        <v>2</v>
+      <c r="F21" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="G21" s="8" t="inlineStr">
         <is>
@@ -1094,7 +1090,7 @@
       </c>
       <c r="H21" s="8" t="inlineStr">
         <is>
-          <t>global:1.0-14.0</t>
+          <t>wc_ratio=1.00</t>
         </is>
       </c>
       <c r="I21" s="8" t="n"/>
@@ -1121,17 +1117,17 @@
       <c r="E22" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F22" s="11" t="n">
-        <v>2</v>
+      <c r="F22" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="G22" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H22" s="8" t="inlineStr">
         <is>
-          <t>1.0-3.0</t>
+          <t>ratio=1.00 (0.50-5.00)</t>
         </is>
       </c>
       <c r="I22" s="8" t="n"/>
@@ -1158,17 +1154,17 @@
       <c r="E23" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F23" s="11" t="n">
-        <v>3</v>
+      <c r="F23" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="G23" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H23" s="8" t="inlineStr">
         <is>
-          <t>2.0-4.0</t>
+          <t>ratio=1.00 (0.33-1.50)</t>
         </is>
       </c>
       <c r="I23" s="8" t="n"/>
@@ -1212,8 +1208,8 @@
       <c r="E25" s="8" t="n">
         <v>2</v>
       </c>
-      <c r="F25" s="10" t="n">
-        <v>1.5</v>
+      <c r="F25" s="9" t="n">
+        <v>3</v>
       </c>
       <c r="G25" s="8" t="inlineStr">
         <is>
@@ -1222,7 +1218,7 @@
       </c>
       <c r="H25" s="8" t="inlineStr">
         <is>
-          <t>0.5-1.5</t>
+          <t>ratio=1.50 (1.00-1.50)</t>
         </is>
       </c>
       <c r="I25" s="8" t="n"/>
@@ -1249,7 +1245,7 @@
       <c r="E26" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F26" s="9" t="n">
+      <c r="F26" s="10" t="n">
         <v>1</v>
       </c>
       <c r="G26" s="8" t="inlineStr">
@@ -1259,7 +1255,7 @@
       </c>
       <c r="H26" s="8" t="inlineStr">
         <is>
-          <t>global:0.5-8.0</t>
+          <t>wc_ratio=1.00</t>
         </is>
       </c>
       <c r="I26" s="8" t="n"/>
@@ -1286,17 +1282,17 @@
       <c r="E27" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F27" s="11" t="n">
-        <v>1.5</v>
+      <c r="F27" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="G27" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H27" s="8" t="inlineStr">
         <is>
-          <t>1.0-2.0</t>
+          <t>ratio=1.00 (1.00-2.00)</t>
         </is>
       </c>
       <c r="I27" s="8" t="n"/>
@@ -1323,17 +1319,17 @@
       <c r="E28" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F28" s="11" t="n">
-        <v>1.5</v>
+      <c r="F28" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="G28" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H28" s="8" t="inlineStr">
         <is>
-          <t>1.0-2.0</t>
+          <t>ratio=1.00 (1.00-1.50)</t>
         </is>
       </c>
       <c r="I28" s="8" t="n"/>
@@ -1378,12 +1374,12 @@
       <c r="F30" s="8" t="n"/>
       <c r="G30" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H30" s="8" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I30" s="8" t="n"/>
@@ -1410,8 +1406,8 @@
       <c r="E31" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F31" s="10" t="n">
-        <v>4</v>
+      <c r="F31" s="9" t="n">
+        <v>0.9</v>
       </c>
       <c r="G31" s="8" t="inlineStr">
         <is>
@@ -1420,7 +1416,7 @@
       </c>
       <c r="H31" s="8" t="inlineStr">
         <is>
-          <t>1.5-8.5</t>
+          <t>ratio=0.90 (0.50-1.12)</t>
         </is>
       </c>
       <c r="I31" s="8" t="n"/>
@@ -1447,17 +1443,17 @@
       <c r="E32" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="F32" s="10" t="n">
-        <v>1</v>
+      <c r="F32" s="11" t="n">
+        <v>2.6</v>
       </c>
       <c r="G32" s="8" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="H32" s="8" t="inlineStr">
         <is>
-          <t>1.0-3.0</t>
+          <t>ratio=0.88 (n=2)</t>
         </is>
       </c>
       <c r="I32" s="8" t="n"/>
@@ -1482,17 +1478,15 @@
         </is>
       </c>
       <c r="E33" s="8" t="n"/>
-      <c r="F33" s="9" t="n">
-        <v>1</v>
-      </c>
+      <c r="F33" s="8" t="n"/>
       <c r="G33" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H33" s="8" t="inlineStr">
         <is>
-          <t>global:1.0-1.5</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I33" s="8" t="n"/>
@@ -1519,17 +1513,17 @@
       <c r="E34" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F34" s="11" t="n">
-        <v>5.8</v>
+      <c r="F34" s="9" t="n">
+        <v>1.7</v>
       </c>
       <c r="G34" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H34" s="8" t="inlineStr">
         <is>
-          <t>1.5-10.0</t>
+          <t>ratio=1.67 (0.33-2.25)</t>
         </is>
       </c>
       <c r="I34" s="8" t="n"/>
@@ -1556,8 +1550,8 @@
       <c r="E35" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="F35" s="10" t="n">
-        <v>4</v>
+      <c r="F35" s="9" t="n">
+        <v>3.8</v>
       </c>
       <c r="G35" s="8" t="inlineStr">
         <is>
@@ -1566,7 +1560,7 @@
       </c>
       <c r="H35" s="8" t="inlineStr">
         <is>
-          <t>2.5-9.5</t>
+          <t>ratio=1.25 (0.62-1.60)</t>
         </is>
       </c>
       <c r="I35" s="8" t="n"/>
@@ -1593,7 +1587,7 @@
       <c r="E36" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F36" s="10" t="n">
+      <c r="F36" s="9" t="n">
         <v>1.5</v>
       </c>
       <c r="G36" s="8" t="inlineStr">
@@ -1603,7 +1597,7 @@
       </c>
       <c r="H36" s="8" t="inlineStr">
         <is>
-          <t>1.0-2.0</t>
+          <t>ratio=1.50 (1.00-3.00)</t>
         </is>
       </c>
       <c r="I36" s="8" t="n"/>
@@ -1647,8 +1641,8 @@
       <c r="E38" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="F38" s="10" t="n">
-        <v>5.5</v>
+      <c r="F38" s="9" t="n">
+        <v>4.3</v>
       </c>
       <c r="G38" s="8" t="inlineStr">
         <is>
@@ -1657,7 +1651,7 @@
       </c>
       <c r="H38" s="8" t="inlineStr">
         <is>
-          <t>4.0-8.5</t>
+          <t>ratio=0.86 (0.42-1.38)</t>
         </is>
       </c>
       <c r="I38" s="8" t="n"/>
@@ -1684,8 +1678,8 @@
       <c r="E39" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F39" s="10" t="n">
-        <v>3.5</v>
+      <c r="F39" s="9" t="n">
+        <v>1.7</v>
       </c>
       <c r="G39" s="8" t="inlineStr">
         <is>
@@ -1694,7 +1688,7 @@
       </c>
       <c r="H39" s="8" t="inlineStr">
         <is>
-          <t>1.5-7.0</t>
+          <t>ratio=1.67 (0.33-2.33)</t>
         </is>
       </c>
       <c r="I39" s="8" t="n"/>
@@ -1721,8 +1715,8 @@
       <c r="E40" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="F40" s="10" t="n">
-        <v>5</v>
+      <c r="F40" s="9" t="n">
+        <v>3</v>
       </c>
       <c r="G40" s="8" t="inlineStr">
         <is>
@@ -1731,7 +1725,7 @@
       </c>
       <c r="H40" s="8" t="inlineStr">
         <is>
-          <t>2.0-10.0</t>
+          <t>ratio=1.00 (0.30-1.25)</t>
         </is>
       </c>
       <c r="I40" s="8" t="n"/>
@@ -1758,8 +1752,8 @@
       <c r="E41" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F41" s="10" t="n">
-        <v>0.8</v>
+      <c r="F41" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="G41" s="8" t="inlineStr">
         <is>
@@ -1768,7 +1762,7 @@
       </c>
       <c r="H41" s="8" t="inlineStr">
         <is>
-          <t>0.5-1.0</t>
+          <t>ratio=1.00 (0.50-1.00)</t>
         </is>
       </c>
       <c r="I41" s="8" t="n"/>
@@ -1813,7 +1807,7 @@
         <v>1</v>
       </c>
       <c r="F43" s="11" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="G43" s="8" t="inlineStr">
         <is>
@@ -1822,7 +1816,7 @@
       </c>
       <c r="H43" s="8" t="inlineStr">
         <is>
-          <t>0.5-1.0</t>
+          <t>ratio=1.00 (n=1)</t>
         </is>
       </c>
       <c r="I43" s="8" t="n"/>
@@ -1847,17 +1841,15 @@
         </is>
       </c>
       <c r="E44" s="8" t="n"/>
-      <c r="F44" s="9" t="n">
-        <v>3</v>
-      </c>
+      <c r="F44" s="8" t="n"/>
       <c r="G44" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H44" s="8" t="inlineStr">
         <is>
-          <t>global:1.5-4.5</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I44" s="8" t="n"/>
@@ -1885,12 +1877,12 @@
       <c r="F45" s="8" t="n"/>
       <c r="G45" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H45" s="8" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I45" s="8" t="n"/>
@@ -1934,8 +1926,8 @@
       <c r="E47" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F47" s="10" t="n">
-        <v>2</v>
+      <c r="F47" s="9" t="n">
+        <v>1</v>
       </c>
       <c r="G47" s="8" t="inlineStr">
         <is>
@@ -1944,7 +1936,7 @@
       </c>
       <c r="H47" s="8" t="inlineStr">
         <is>
-          <t>1.0-2.0</t>
+          <t>ratio=1.00 (0.62-1.50)</t>
         </is>
       </c>
       <c r="I47" s="8" t="n"/>
@@ -1971,8 +1963,8 @@
       <c r="E48" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="F48" s="10" t="n">
-        <v>6</v>
+      <c r="F48" s="9" t="n">
+        <v>8.6</v>
       </c>
       <c r="G48" s="8" t="inlineStr">
         <is>
@@ -1981,7 +1973,7 @@
       </c>
       <c r="H48" s="8" t="inlineStr">
         <is>
-          <t>3.0-8.0</t>
+          <t>ratio=1.71 (0.50-2.62)</t>
         </is>
       </c>
       <c r="I48" s="8" t="n"/>
@@ -2009,12 +2001,12 @@
       <c r="F49" s="8" t="n"/>
       <c r="G49" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H49" s="8" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I49" s="8" t="n"/>
@@ -2042,12 +2034,12 @@
       <c r="F50" s="8" t="n"/>
       <c r="G50" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H50" s="8" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I50" s="8" t="n"/>
@@ -2074,8 +2066,8 @@
       <c r="E51" s="8" t="n">
         <v>5</v>
       </c>
-      <c r="F51" s="10" t="n">
-        <v>6</v>
+      <c r="F51" s="9" t="n">
+        <v>5</v>
       </c>
       <c r="G51" s="8" t="inlineStr">
         <is>
@@ -2084,7 +2076,7 @@
       </c>
       <c r="H51" s="8" t="inlineStr">
         <is>
-          <t>1.5-7.0</t>
+          <t>ratio=1.00 (0.36-1.33)</t>
         </is>
       </c>
       <c r="I51" s="8" t="n"/>
@@ -2112,12 +2104,12 @@
       <c r="F52" s="8" t="n"/>
       <c r="G52" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H52" s="8" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I52" s="8" t="n"/>
@@ -2161,8 +2153,8 @@
       <c r="E54" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F54" s="10" t="n">
-        <v>2.2</v>
+      <c r="F54" s="9" t="n">
+        <v>2</v>
       </c>
       <c r="G54" s="8" t="inlineStr">
         <is>
@@ -2171,7 +2163,7 @@
       </c>
       <c r="H54" s="8" t="inlineStr">
         <is>
-          <t>1.0-3.0</t>
+          <t>ratio=2.00 (1.00-3.00)</t>
         </is>
       </c>
       <c r="I54" s="8" t="n"/>
@@ -2199,12 +2191,12 @@
       <c r="F55" s="8" t="n"/>
       <c r="G55" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="H55" s="8" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
+          <t>0h estimate</t>
         </is>
       </c>
       <c r="I55" s="8" t="n"/>
@@ -2231,17 +2223,17 @@
       <c r="E56" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F56" s="10" t="n">
-        <v>2.5</v>
+      <c r="F56" s="11" t="n">
+        <v>3.2</v>
       </c>
       <c r="G56" s="8" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="H56" s="8" t="inlineStr">
         <is>
-          <t>2.0-3.0</t>
+          <t>ratio=3.25 (n=2)</t>
         </is>
       </c>
       <c r="I56" s="8" t="n"/>
@@ -2255,7 +2247,7 @@
         </is>
       </c>
       <c r="F58" s="1" t="n">
-        <v>94.3</v>
+        <v>68.3</v>
       </c>
     </row>
   </sheetData>
@@ -2323,7 +2315,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>25-034, 23-034, 25-002, 23-035, 25-036</t>
+          <t>24-006, 25-087, 25-042, 23-034, 24-041</t>
         </is>
       </c>
     </row>
@@ -3673,35 +3665,35 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>25-034</t>
+          <t>24-006</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>23-034</t>
+          <t>25-087</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>25-002</t>
+          <t>25-042</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>23-035</t>
+          <t>23-034</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>25-036</t>
+          <t>24-041</t>
         </is>
       </c>
     </row>
@@ -3756,23 +3748,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>global:1.0-1.0</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>global</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3790,19 +3778,15 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>23-034, 23-035, 25-002, 25-034, 25-036</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3825,12 +3809,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1.0-3.5</t>
+          <t>ratio=1.00 (0.67-1.50)</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>25-036, 25-034, 25-002, 23-035, 23-034</t>
+          <t>25-087, 25-042, 24-041, 24-006, 23-034</t>
         </is>
       </c>
     </row>
@@ -3846,7 +3830,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>9</v>
+        <v>4.3</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -3855,12 +3839,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2.0-14.0</t>
+          <t>ratio=1.44 (1.00-2.00)</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>25-036, 25-034, 25-002, 23-035, 23-034</t>
+          <t>25-087, 25-042, 24-041, 24-006, 23-034</t>
         </is>
       </c>
     </row>
@@ -3876,7 +3860,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>6.5</v>
+        <v>2</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -3885,12 +3869,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>2.0-10.5</t>
+          <t>ratio=1.00 (0.29-2.64)</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>25-036, 25-034, 25-002, 23-035, 23-034</t>
+          <t>25-087, 25-042, 24-041, 24-006, 23-034</t>
         </is>
       </c>
     </row>
@@ -3906,7 +3890,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>2.5</v>
+        <v>0.5</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3915,12 +3899,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>2.0-6.5</t>
+          <t>ratio=0.50 (0.20-1.33)</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>25-036, 25-034, 25-002</t>
+          <t>25-087, 25-042, 24-041</t>
         </is>
       </c>
     </row>
@@ -3936,7 +3920,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>3</v>
+        <v>4.2</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3945,12 +3929,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2.0-4.0</t>
+          <t>ratio=0.83 (0.50-1.12)</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>25-002, 23-035, 23-034</t>
+          <t>25-087, 25-042, 24-041, 24-006, 23-034</t>
         </is>
       </c>
     </row>
@@ -3975,12 +3959,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.0-1.0</t>
+          <t>ratio=1.00 (1.00-1.00)</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>25-036, 25-034, 25-002, 23-035</t>
+          <t>25-087, 25-042, 24-041</t>
         </is>
       </c>
     </row>
@@ -3996,23 +3980,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>global:1.0-2.0</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>global</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -4026,21 +4006,21 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1.2</v>
+        <v>3</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1.0-1.5</t>
+          <t>ratio=1.50 (1.00-3.00)</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>23-035, 23-034</t>
+          <t>25-087, 25-042, 24-041, 24-006, 23-034</t>
         </is>
       </c>
     </row>
@@ -4056,7 +4036,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -4065,12 +4045,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>global:1.0-14.0</t>
+          <t>wc_ratio=1.00</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>global</t>
+          <t>wc_avg</t>
         </is>
       </c>
     </row>
@@ -4086,21 +4066,21 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.0-3.0</t>
+          <t>ratio=1.00 (0.50-5.00)</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>23-035, 23-034</t>
+          <t>25-087, 25-042, 24-041, 24-006, 23-034</t>
         </is>
       </c>
     </row>
@@ -4116,21 +4096,21 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>2.0-4.0</t>
+          <t>ratio=1.00 (0.33-1.50)</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>23-035, 23-034</t>
+          <t>25-087, 25-042, 24-041, 24-006, 23-034</t>
         </is>
       </c>
     </row>
@@ -4146,23 +4126,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>global:1.0-2.0</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>global</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -4176,7 +4152,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4185,12 +4161,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0.5-1.5</t>
+          <t>ratio=1.50 (1.00-1.50)</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>25-036, 23-035, 23-034</t>
+          <t>25-087, 25-042, 24-006, 23-034</t>
         </is>
       </c>
     </row>
@@ -4215,12 +4191,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>global:0.5-8.0</t>
+          <t>wc_ratio=1.00</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>global</t>
+          <t>wc_avg</t>
         </is>
       </c>
     </row>
@@ -4236,21 +4212,21 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1.0-2.0</t>
+          <t>ratio=1.00 (1.00-2.00)</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>23-035, 23-034</t>
+          <t>25-087, 25-042, 24-041, 24-006, 23-034</t>
         </is>
       </c>
     </row>
@@ -4266,21 +4242,21 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1.0-2.0</t>
+          <t>ratio=1.00 (1.00-1.50)</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>23-035, 23-034</t>
+          <t>25-087, 25-042, 24-041, 24-006, 23-034</t>
         </is>
       </c>
     </row>
@@ -4300,19 +4276,15 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>23-034, 23-035</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -4326,7 +4298,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>4</v>
+        <v>0.9</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4335,12 +4307,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.5-8.5</t>
+          <t>ratio=0.90 (0.50-1.12)</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>25-036, 25-034, 25-002, 23-035, 23-034</t>
+          <t>25-087, 25-042, 24-041, 24-006, 23-034</t>
         </is>
       </c>
     </row>
@@ -4356,21 +4328,21 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1</v>
+        <v>2.6</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1.0-3.0</t>
+          <t>ratio=0.88 (n=2)</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>25-036, 25-034, 25-002, 23-035, 23-034</t>
+          <t>24-041, 23-034</t>
         </is>
       </c>
     </row>
@@ -4386,23 +4358,19 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>global:1.0-1.5</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>global</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -4416,21 +4384,21 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>5.8</v>
+        <v>1.7</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1.5-10.0</t>
+          <t>ratio=1.67 (0.33-2.25)</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>23-035, 23-034</t>
+          <t>25-087, 25-042, 24-041, 24-006, 23-034</t>
         </is>
       </c>
     </row>
@@ -4446,7 +4414,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4455,12 +4423,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>2.5-9.5</t>
+          <t>ratio=1.25 (0.62-1.60)</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>25-036, 25-034, 23-035, 23-034</t>
+          <t>25-087, 25-042, 24-041, 24-006, 23-034</t>
         </is>
       </c>
     </row>
@@ -4485,12 +4453,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1.0-2.0</t>
+          <t>ratio=1.50 (1.00-3.00)</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>25-036, 25-034, 25-002, 23-035, 23-034</t>
+          <t>25-087, 25-042, 24-041, 24-006, 23-034</t>
         </is>
       </c>
     </row>
@@ -4506,7 +4474,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>5.5</v>
+        <v>4.3</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4515,12 +4483,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>4.0-8.5</t>
+          <t>ratio=0.86 (0.42-1.38)</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>25-034, 25-002, 23-035, 23-034</t>
+          <t>25-087, 25-042, 24-041, 24-006, 23-034</t>
         </is>
       </c>
     </row>
@@ -4536,7 +4504,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>3.5</v>
+        <v>1.7</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4545,12 +4513,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1.5-7.0</t>
+          <t>ratio=1.67 (0.33-2.33)</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>25-036, 25-034, 25-002, 23-035, 23-034</t>
+          <t>25-087, 25-042, 24-041, 23-034</t>
         </is>
       </c>
     </row>
@@ -4566,7 +4534,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4575,12 +4543,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>2.0-10.0</t>
+          <t>ratio=1.00 (0.30-1.25)</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>25-036, 25-034, 25-002, 23-035, 23-034</t>
+          <t>25-087, 25-042, 24-041, 23-034</t>
         </is>
       </c>
     </row>
@@ -4596,7 +4564,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4605,12 +4573,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>0.5-1.0</t>
+          <t>ratio=1.00 (0.50-1.00)</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>25-036, 25-034, 25-002, 23-035, 23-034</t>
+          <t>25-087, 25-042, 24-041, 24-006, 23-034</t>
         </is>
       </c>
     </row>
@@ -4626,7 +4594,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4635,12 +4603,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>0.5-1.0</t>
+          <t>ratio=1.00 (n=1)</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>25-036, 25-034, 25-002, 23-035, 23-034</t>
+          <t>23-034</t>
         </is>
       </c>
     </row>
@@ -4656,23 +4624,19 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>global:1.5-4.5</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>global</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -4690,19 +4654,15 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>23-034, 23-035</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -4716,7 +4676,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4725,12 +4685,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1.0-2.0</t>
+          <t>ratio=1.00 (0.62-1.50)</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>25-036, 25-034, 25-002, 23-035, 23-034</t>
+          <t>25-042, 24-041, 23-034</t>
         </is>
       </c>
     </row>
@@ -4746,7 +4706,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>6</v>
+        <v>8.6</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4755,12 +4715,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>3.0-8.0</t>
+          <t>ratio=1.71 (0.50-2.62)</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>25-036, 25-034, 25-002, 23-035, 23-034</t>
+          <t>25-087, 25-042, 24-041, 24-006, 23-034</t>
         </is>
       </c>
     </row>
@@ -4780,19 +4740,15 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>23-034, 23-035, 25-002, 25-034, 25-036</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -4810,19 +4766,15 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>23-034, 23-035</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -4836,7 +4788,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4845,12 +4797,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1.5-7.0</t>
+          <t>ratio=1.00 (0.36-1.33)</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>25-036, 25-034, 25-002, 23-035, 23-034</t>
+          <t>25-087, 25-042, 24-041, 24-006, 23-034</t>
         </is>
       </c>
     </row>
@@ -4870,19 +4822,15 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>23-034, 23-035, 25-002, 25-034, 25-036</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -4896,7 +4844,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4905,12 +4853,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>1.0-3.0</t>
+          <t>ratio=2.00 (1.00-3.00)</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>25-036, 25-034, 23-035, 23-034</t>
+          <t>25-087, 25-042, 24-041, 24-006, 23-034</t>
         </is>
       </c>
     </row>
@@ -4930,19 +4878,15 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>skip</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>est:0.0-0.0</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>23-034, 23-035, 25-002, 25-034, 25-036</t>
-        </is>
-      </c>
+          <t>0h estimate</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -4956,21 +4900,21 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>2.5</v>
+        <v>3.2</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>2.0-3.0</t>
+          <t>ratio=3.25 (n=2)</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>25-036, 25-034, 25-002, 23-035, 23-034</t>
+          <t>25-087, 24-041</t>
         </is>
       </c>
     </row>

--- a/buildplan_generator/output/25-088 GENERATED BUILD PLAN.xlsx
+++ b/buildplan_generator/output/25-088 GENERATED BUILD PLAN.xlsx
@@ -543,7 +543,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>24-006, 25-087, 25-042, 23-034, 24-041</t>
+          <t>25-042, 23-034, 24-006, 25-087, 24-041</t>
         </is>
       </c>
     </row>
@@ -2315,7 +2315,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>24-006, 25-087, 25-042, 23-034, 24-041</t>
+          <t>25-042, 23-034, 24-006, 25-087, 24-041</t>
         </is>
       </c>
     </row>
@@ -3665,28 +3665,28 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>24-006</t>
+          <t>25-042</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>25-087</t>
+          <t>23-034</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>25-042</t>
+          <t>24-006</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>23-034</t>
+          <t>25-087</t>
         </is>
       </c>
     </row>

--- a/buildplan_generator/output/25-088 GENERATED BUILD PLAN.xlsx
+++ b/buildplan_generator/output/25-088 GENERATED BUILD PLAN.xlsx
@@ -53,7 +53,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -84,12 +84,6 @@
         <bgColor rgb="00FCE4EC"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-        <bgColor rgb="00FFF2CC"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -109,7 +103,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -123,7 +117,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -543,7 +536,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>25-042, 23-034, 24-006, 25-087, 24-041</t>
+          <t>24-006, 25-025, 25-087, 25-026, 25-085</t>
         </is>
       </c>
     </row>
@@ -638,12 +631,12 @@
       <c r="F6" s="8" t="n"/>
       <c r="G6" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H6" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I6" s="8" t="n"/>
@@ -671,12 +664,12 @@
       <c r="F7" s="8" t="n"/>
       <c r="G7" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H7" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I7" s="8" t="n"/>
@@ -721,7 +714,7 @@
         <v>2</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="G9" s="8" t="inlineStr">
         <is>
@@ -730,7 +723,7 @@
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.67-1.50)</t>
+          <t>group_total:2h</t>
         </is>
       </c>
       <c r="I9" s="8" t="n"/>
@@ -758,7 +751,7 @@
         <v>3</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>4.3</v>
+        <v>1.3</v>
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
@@ -767,7 +760,7 @@
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.44 (1.00-2.00)</t>
+          <t>group_total:2h</t>
         </is>
       </c>
       <c r="I10" s="8" t="n"/>
@@ -812,7 +805,7 @@
         <v>2</v>
       </c>
       <c r="F12" s="9" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
@@ -821,7 +814,7 @@
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.29-2.64)</t>
+          <t>group_total:3h</t>
         </is>
       </c>
       <c r="I12" s="8" t="n"/>
@@ -849,7 +842,7 @@
         <v>1</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="G13" s="8" t="inlineStr">
         <is>
@@ -858,7 +851,7 @@
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.50 (0.20-1.33)</t>
+          <t>group_total:3h</t>
         </is>
       </c>
       <c r="I13" s="8" t="n"/>
@@ -903,7 +896,7 @@
         <v>5</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>4.2</v>
+        <v>2.9</v>
       </c>
       <c r="G15" s="8" t="inlineStr">
         <is>
@@ -912,7 +905,7 @@
       </c>
       <c r="H15" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.83 (0.50-1.12)</t>
+          <t>group_total:3h</t>
         </is>
       </c>
       <c r="I15" s="8" t="n"/>
@@ -957,7 +950,7 @@
         <v>1</v>
       </c>
       <c r="F17" s="9" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="G17" s="8" t="inlineStr">
         <is>
@@ -966,7 +959,7 @@
       </c>
       <c r="H17" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (1.00-1.00)</t>
+          <t>group_total:1h</t>
         </is>
       </c>
       <c r="I17" s="8" t="n"/>
@@ -1011,12 +1004,12 @@
       <c r="F19" s="8" t="n"/>
       <c r="G19" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H19" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I19" s="8" t="n"/>
@@ -1044,7 +1037,7 @@
         <v>2</v>
       </c>
       <c r="F20" s="9" t="n">
-        <v>3</v>
+        <v>0.9</v>
       </c>
       <c r="G20" s="8" t="inlineStr">
         <is>
@@ -1053,7 +1046,7 @@
       </c>
       <c r="H20" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.50 (1.00-3.00)</t>
+          <t>group_total:4h</t>
         </is>
       </c>
       <c r="I20" s="8" t="n"/>
@@ -1080,17 +1073,17 @@
       <c r="E21" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F21" s="10" t="n">
-        <v>1</v>
+      <c r="F21" s="9" t="n">
+        <v>0.1</v>
       </c>
       <c r="G21" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H21" s="8" t="inlineStr">
         <is>
-          <t>wc_ratio=1.00</t>
+          <t>group_total:4h</t>
         </is>
       </c>
       <c r="I21" s="8" t="n"/>
@@ -1118,7 +1111,7 @@
         <v>1</v>
       </c>
       <c r="F22" s="9" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="G22" s="8" t="inlineStr">
         <is>
@@ -1127,7 +1120,7 @@
       </c>
       <c r="H22" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.50-5.00)</t>
+          <t>group_total:4h</t>
         </is>
       </c>
       <c r="I22" s="8" t="n"/>
@@ -1155,7 +1148,7 @@
         <v>2</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="G23" s="8" t="inlineStr">
         <is>
@@ -1164,7 +1157,7 @@
       </c>
       <c r="H23" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.33-1.50)</t>
+          <t>group_total:4h</t>
         </is>
       </c>
       <c r="I23" s="8" t="n"/>
@@ -1209,7 +1202,7 @@
         <v>2</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="G25" s="8" t="inlineStr">
         <is>
@@ -1218,7 +1211,7 @@
       </c>
       <c r="H25" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.50 (1.00-1.50)</t>
+          <t>group_total:1h</t>
         </is>
       </c>
       <c r="I25" s="8" t="n"/>
@@ -1245,17 +1238,17 @@
       <c r="E26" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F26" s="10" t="n">
-        <v>1</v>
+      <c r="F26" s="9" t="n">
+        <v>0.1</v>
       </c>
       <c r="G26" s="8" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H26" s="8" t="inlineStr">
         <is>
-          <t>wc_ratio=1.00</t>
+          <t>group_total:1h</t>
         </is>
       </c>
       <c r="I26" s="8" t="n"/>
@@ -1283,7 +1276,7 @@
         <v>1</v>
       </c>
       <c r="F27" s="9" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="G27" s="8" t="inlineStr">
         <is>
@@ -1292,7 +1285,7 @@
       </c>
       <c r="H27" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (1.00-2.00)</t>
+          <t>group_total:1h</t>
         </is>
       </c>
       <c r="I27" s="8" t="n"/>
@@ -1320,7 +1313,7 @@
         <v>1</v>
       </c>
       <c r="F28" s="9" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="G28" s="8" t="inlineStr">
         <is>
@@ -1329,7 +1322,7 @@
       </c>
       <c r="H28" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (1.00-1.50)</t>
+          <t>group_total:1h</t>
         </is>
       </c>
       <c r="I28" s="8" t="n"/>
@@ -1374,12 +1367,12 @@
       <c r="F30" s="8" t="n"/>
       <c r="G30" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H30" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I30" s="8" t="n"/>
@@ -1407,7 +1400,7 @@
         <v>1</v>
       </c>
       <c r="F31" s="9" t="n">
-        <v>0.9</v>
+        <v>4.1</v>
       </c>
       <c r="G31" s="8" t="inlineStr">
         <is>
@@ -1416,7 +1409,7 @@
       </c>
       <c r="H31" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.90 (0.50-1.12)</t>
+          <t>group_total:13h</t>
         </is>
       </c>
       <c r="I31" s="8" t="n"/>
@@ -1443,17 +1436,17 @@
       <c r="E32" s="8" t="n">
         <v>3</v>
       </c>
-      <c r="F32" s="11" t="n">
-        <v>2.6</v>
+      <c r="F32" s="9" t="n">
+        <v>0.9</v>
       </c>
       <c r="G32" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H32" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.88 (n=2)</t>
+          <t>group_total:13h</t>
         </is>
       </c>
       <c r="I32" s="8" t="n"/>
@@ -1481,12 +1474,12 @@
       <c r="F33" s="8" t="n"/>
       <c r="G33" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H33" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I33" s="8" t="n"/>
@@ -1514,7 +1507,7 @@
         <v>1</v>
       </c>
       <c r="F34" s="9" t="n">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="G34" s="8" t="inlineStr">
         <is>
@@ -1523,7 +1516,7 @@
       </c>
       <c r="H34" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.67 (0.33-2.25)</t>
+          <t>group_total:13h</t>
         </is>
       </c>
       <c r="I34" s="8" t="n"/>
@@ -1551,7 +1544,7 @@
         <v>3</v>
       </c>
       <c r="F35" s="9" t="n">
-        <v>3.8</v>
+        <v>5.7</v>
       </c>
       <c r="G35" s="8" t="inlineStr">
         <is>
@@ -1560,7 +1553,7 @@
       </c>
       <c r="H35" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.25 (0.62-1.60)</t>
+          <t>group_total:13h</t>
         </is>
       </c>
       <c r="I35" s="8" t="n"/>
@@ -1587,17 +1580,17 @@
       <c r="E36" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F36" s="9" t="n">
-        <v>1.5</v>
+      <c r="F36" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="G36" s="8" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H36" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.50 (1.00-3.00)</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I36" s="8" t="n"/>
@@ -1642,7 +1635,7 @@
         <v>5</v>
       </c>
       <c r="F38" s="9" t="n">
-        <v>4.3</v>
+        <v>5.6</v>
       </c>
       <c r="G38" s="8" t="inlineStr">
         <is>
@@ -1651,7 +1644,7 @@
       </c>
       <c r="H38" s="8" t="inlineStr">
         <is>
-          <t>ratio=0.86 (0.42-1.38)</t>
+          <t>group_total:15h</t>
         </is>
       </c>
       <c r="I38" s="8" t="n"/>
@@ -1679,7 +1672,7 @@
         <v>1</v>
       </c>
       <c r="F39" s="9" t="n">
-        <v>1.7</v>
+        <v>2.8</v>
       </c>
       <c r="G39" s="8" t="inlineStr">
         <is>
@@ -1688,7 +1681,7 @@
       </c>
       <c r="H39" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.67 (0.33-2.33)</t>
+          <t>group_total:15h</t>
         </is>
       </c>
       <c r="I39" s="8" t="n"/>
@@ -1716,7 +1709,7 @@
         <v>3</v>
       </c>
       <c r="F40" s="9" t="n">
-        <v>3</v>
+        <v>5.5</v>
       </c>
       <c r="G40" s="8" t="inlineStr">
         <is>
@@ -1725,7 +1718,7 @@
       </c>
       <c r="H40" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.30-1.25)</t>
+          <t>group_total:15h</t>
         </is>
       </c>
       <c r="I40" s="8" t="n"/>
@@ -1753,7 +1746,7 @@
         <v>1</v>
       </c>
       <c r="F41" s="9" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="G41" s="8" t="inlineStr">
         <is>
@@ -1762,7 +1755,7 @@
       </c>
       <c r="H41" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.50-1.00)</t>
+          <t>group_total:15h</t>
         </is>
       </c>
       <c r="I41" s="8" t="n"/>
@@ -1806,17 +1799,17 @@
       <c r="E43" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F43" s="11" t="n">
-        <v>1</v>
+      <c r="F43" s="9" t="n">
+        <v>0.6</v>
       </c>
       <c r="G43" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H43" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (n=1)</t>
+          <t>group_total:15h</t>
         </is>
       </c>
       <c r="I43" s="8" t="n"/>
@@ -1844,12 +1837,12 @@
       <c r="F44" s="8" t="n"/>
       <c r="G44" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H44" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I44" s="8" t="n"/>
@@ -1877,12 +1870,12 @@
       <c r="F45" s="8" t="n"/>
       <c r="G45" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H45" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I45" s="8" t="n"/>
@@ -1927,7 +1920,7 @@
         <v>1</v>
       </c>
       <c r="F47" s="9" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="G47" s="8" t="inlineStr">
         <is>
@@ -1936,7 +1929,7 @@
       </c>
       <c r="H47" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.62-1.50)</t>
+          <t>group_total:12h</t>
         </is>
       </c>
       <c r="I47" s="8" t="n"/>
@@ -1964,7 +1957,7 @@
         <v>5</v>
       </c>
       <c r="F48" s="9" t="n">
-        <v>8.6</v>
+        <v>3.2</v>
       </c>
       <c r="G48" s="8" t="inlineStr">
         <is>
@@ -1973,7 +1966,7 @@
       </c>
       <c r="H48" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.71 (0.50-2.62)</t>
+          <t>group_total:12h</t>
         </is>
       </c>
       <c r="I48" s="8" t="n"/>
@@ -2001,12 +1994,12 @@
       <c r="F49" s="8" t="n"/>
       <c r="G49" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H49" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I49" s="8" t="n"/>
@@ -2034,12 +2027,12 @@
       <c r="F50" s="8" t="n"/>
       <c r="G50" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H50" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I50" s="8" t="n"/>
@@ -2067,7 +2060,7 @@
         <v>5</v>
       </c>
       <c r="F51" s="9" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="G51" s="8" t="inlineStr">
         <is>
@@ -2076,7 +2069,7 @@
       </c>
       <c r="H51" s="8" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.36-1.33)</t>
+          <t>group_total:12h</t>
         </is>
       </c>
       <c r="I51" s="8" t="n"/>
@@ -2104,12 +2097,12 @@
       <c r="F52" s="8" t="n"/>
       <c r="G52" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H52" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I52" s="8" t="n"/>
@@ -2154,7 +2147,7 @@
         <v>1</v>
       </c>
       <c r="F54" s="9" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="G54" s="8" t="inlineStr">
         <is>
@@ -2163,7 +2156,7 @@
       </c>
       <c r="H54" s="8" t="inlineStr">
         <is>
-          <t>ratio=2.00 (1.00-3.00)</t>
+          <t>group_total:12h</t>
         </is>
       </c>
       <c r="I54" s="8" t="n"/>
@@ -2191,12 +2184,12 @@
       <c r="F55" s="8" t="n"/>
       <c r="G55" s="8" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H55" s="8" t="inlineStr">
         <is>
-          <t>0h estimate</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I55" s="8" t="n"/>
@@ -2223,17 +2216,17 @@
       <c r="E56" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F56" s="11" t="n">
-        <v>3.2</v>
+      <c r="F56" s="9" t="n">
+        <v>1.3</v>
       </c>
       <c r="G56" s="8" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="H56" s="8" t="inlineStr">
         <is>
-          <t>ratio=3.25 (n=2)</t>
+          <t>group_total:12h</t>
         </is>
       </c>
       <c r="I56" s="8" t="n"/>
@@ -2247,7 +2240,7 @@
         </is>
       </c>
       <c r="F58" s="1" t="n">
-        <v>68.3</v>
+        <v>54.7</v>
       </c>
     </row>
   </sheetData>
@@ -2315,7 +2308,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>25-042, 23-034, 24-006, 25-087, 24-041</t>
+          <t>24-006, 25-025, 25-087, 25-026, 25-085</t>
         </is>
       </c>
     </row>
@@ -3665,35 +3658,35 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>25-042</t>
+          <t>24-006</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>23-034</t>
+          <t>25-025</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>24-006</t>
+          <t>25-087</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>25-087</t>
+          <t>25-026</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>24-041</t>
+          <t>25-085</t>
         </is>
       </c>
     </row>
@@ -3752,15 +3745,19 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -3778,15 +3775,19 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -3800,7 +3801,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>2</v>
+        <v>0.6</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -3809,12 +3810,12 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.67-1.50)</t>
+          <t>group_total:2h</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>25-087, 25-042, 24-041, 24-006, 23-034</t>
+          <t>model(NOZZLES)</t>
         </is>
       </c>
     </row>
@@ -3830,7 +3831,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>4.3</v>
+        <v>1.3</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -3839,12 +3840,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ratio=1.44 (1.00-2.00)</t>
+          <t>group_total:2h</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>25-087, 25-042, 24-041, 24-006, 23-034</t>
+          <t>model(NOZZLES)</t>
         </is>
       </c>
     </row>
@@ -3860,7 +3861,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -3869,12 +3870,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.29-2.64)</t>
+          <t>group_total:3h</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>25-087, 25-042, 24-041, 24-006, 23-034</t>
+          <t>model(CUT_PREP)</t>
         </is>
       </c>
     </row>
@@ -3890,7 +3891,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3899,12 +3900,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>ratio=0.50 (0.20-1.33)</t>
+          <t>group_total:3h</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>25-087, 25-042, 24-041</t>
+          <t>model(CUT_PREP)</t>
         </is>
       </c>
     </row>
@@ -3920,7 +3921,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>4.2</v>
+        <v>2.9</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3929,12 +3930,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>ratio=0.83 (0.50-1.12)</t>
+          <t>group_total:3h</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>25-087, 25-042, 24-041, 24-006, 23-034</t>
+          <t>model(SUPPORTS)</t>
         </is>
       </c>
     </row>
@@ -3950,7 +3951,7 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -3959,12 +3960,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>ratio=1.00 (1.00-1.00)</t>
+          <t>group_total:1h</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>25-087, 25-042, 24-041</t>
+          <t>model(MISC_PARTS)</t>
         </is>
       </c>
     </row>
@@ -3984,15 +3985,19 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -4006,7 +4011,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>3</v>
+        <v>0.9</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -4015,12 +4020,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>ratio=1.50 (1.00-3.00)</t>
+          <t>group_total:4h</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>25-087, 25-042, 24-041, 24-006, 23-034</t>
+          <t>model(TOP_HEAD)</t>
         </is>
       </c>
     </row>
@@ -4036,21 +4041,21 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>wc_ratio=1.00</t>
+          <t>group_total:4h</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>wc_avg</t>
+          <t>model(TOP_HEAD)</t>
         </is>
       </c>
     </row>
@@ -4066,7 +4071,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -4075,12 +4080,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.50-5.00)</t>
+          <t>group_total:4h</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>25-087, 25-042, 24-041, 24-006, 23-034</t>
+          <t>model(TOP_HEAD)</t>
         </is>
       </c>
     </row>
@@ -4096,7 +4101,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4105,12 +4110,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.33-1.50)</t>
+          <t>group_total:4h</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>25-087, 25-042, 24-041, 24-006, 23-034</t>
+          <t>model(TOP_HEAD)</t>
         </is>
       </c>
     </row>
@@ -4130,15 +4135,19 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -4152,7 +4161,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4161,12 +4170,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>ratio=1.50 (1.00-1.50)</t>
+          <t>group_total:1h</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>25-087, 25-042, 24-006, 23-034</t>
+          <t>model(BTM_HEAD)</t>
         </is>
       </c>
     </row>
@@ -4182,21 +4191,21 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>wc_ratio=1.00</t>
+          <t>group_total:1h</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>wc_avg</t>
+          <t>model(BTM_HEAD)</t>
         </is>
       </c>
     </row>
@@ -4212,7 +4221,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4221,12 +4230,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>ratio=1.00 (1.00-2.00)</t>
+          <t>group_total:1h</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>25-087, 25-042, 24-041, 24-006, 23-034</t>
+          <t>model(BTM_HEAD)</t>
         </is>
       </c>
     </row>
@@ -4242,7 +4251,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4251,12 +4260,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>ratio=1.00 (1.00-1.50)</t>
+          <t>group_total:1h</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>25-087, 25-042, 24-041, 24-006, 23-034</t>
+          <t>model(BTM_HEAD)</t>
         </is>
       </c>
     </row>
@@ -4276,15 +4285,19 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -4298,7 +4311,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>0.9</v>
+        <v>4.1</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4307,12 +4320,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>ratio=0.90 (0.50-1.12)</t>
+          <t>group_total:13h</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>25-087, 25-042, 24-041, 24-006, 23-034</t>
+          <t>model(FIT_ASSEMBLY)</t>
         </is>
       </c>
     </row>
@@ -4328,21 +4341,21 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>2.6</v>
+        <v>0.9</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>ratio=0.88 (n=2)</t>
+          <t>group_total:13h</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>24-041, 23-034</t>
+          <t>model(FIT_ASSEMBLY)</t>
         </is>
       </c>
     </row>
@@ -4362,15 +4375,19 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -4384,7 +4401,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>1.7</v>
+        <v>2.5</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4393,12 +4410,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>ratio=1.67 (0.33-2.25)</t>
+          <t>group_total:13h</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>25-087, 25-042, 24-041, 24-006, 23-034</t>
+          <t>model(FIT_ASSEMBLY)</t>
         </is>
       </c>
     </row>
@@ -4414,7 +4431,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>3.8</v>
+        <v>5.7</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4423,12 +4440,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>ratio=1.25 (0.62-1.60)</t>
+          <t>group_total:13h</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>25-087, 25-042, 24-041, 24-006, 23-034</t>
+          <t>model(FIT_ASSEMBLY)</t>
         </is>
       </c>
     </row>
@@ -4444,21 +4461,21 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>ratio=1.50 (1.00-3.00)</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>25-087, 25-042, 24-041, 24-006, 23-034</t>
+          <t>nan</t>
         </is>
       </c>
     </row>
@@ -4474,7 +4491,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>4.3</v>
+        <v>5.6</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4483,12 +4500,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>ratio=0.86 (0.42-1.38)</t>
+          <t>group_total:15h</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>25-087, 25-042, 24-041, 24-006, 23-034</t>
+          <t>model(DETAIL_EXT)</t>
         </is>
       </c>
     </row>
@@ -4504,7 +4521,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>1.7</v>
+        <v>2.8</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4513,12 +4530,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>ratio=1.67 (0.33-2.33)</t>
+          <t>group_total:15h</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>25-087, 25-042, 24-041, 23-034</t>
+          <t>model(DETAIL_EXT)</t>
         </is>
       </c>
     </row>
@@ -4534,7 +4551,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>3</v>
+        <v>5.5</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4543,12 +4560,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.30-1.25)</t>
+          <t>group_total:15h</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>25-087, 25-042, 24-041, 23-034</t>
+          <t>model(DETAIL_EXT)</t>
         </is>
       </c>
     </row>
@@ -4564,7 +4581,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4573,12 +4590,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.50-1.00)</t>
+          <t>group_total:15h</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>25-087, 25-042, 24-041, 24-006, 23-034</t>
+          <t>model(DETAIL_EXT)</t>
         </is>
       </c>
     </row>
@@ -4594,21 +4611,21 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>ratio=1.00 (n=1)</t>
+          <t>group_total:15h</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>23-034</t>
+          <t>model(DETAIL_EXT)</t>
         </is>
       </c>
     </row>
@@ -4628,15 +4645,19 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -4654,15 +4675,19 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -4676,7 +4701,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4685,12 +4710,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.62-1.50)</t>
+          <t>group_total:12h</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>25-042, 24-041, 23-034</t>
+          <t>model(TEST_CLEAN)</t>
         </is>
       </c>
     </row>
@@ -4706,7 +4731,7 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>8.6</v>
+        <v>3.2</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4715,12 +4740,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>ratio=1.71 (0.50-2.62)</t>
+          <t>group_total:12h</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>25-087, 25-042, 24-041, 24-006, 23-034</t>
+          <t>model(TEST_CLEAN)</t>
         </is>
       </c>
     </row>
@@ -4740,15 +4765,19 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -4766,15 +4795,19 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -4788,7 +4821,7 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4797,12 +4830,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>ratio=1.00 (0.36-1.33)</t>
+          <t>group_total:12h</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>25-087, 25-042, 24-041, 24-006, 23-034</t>
+          <t>model(TEST_CLEAN)</t>
         </is>
       </c>
     </row>
@@ -4822,15 +4855,19 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -4844,7 +4881,7 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>2</v>
+        <v>1.1</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4853,12 +4890,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>ratio=2.00 (1.00-3.00)</t>
+          <t>group_total:12h</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>25-087, 25-042, 24-041, 24-006, 23-034</t>
+          <t>model(TEST_CLEAN)</t>
         </is>
       </c>
     </row>
@@ -4878,15 +4915,19 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>skip</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>0h estimate</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr"/>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -4900,21 +4941,21 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>3.2</v>
+        <v>1.3</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>ratio=3.25 (n=2)</t>
+          <t>group_total:12h</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>25-087, 24-041</t>
+          <t>model(TEST_CLEAN)</t>
         </is>
       </c>
     </row>

--- a/buildplan_generator/output/25-088 GENERATED BUILD PLAN.xlsx
+++ b/buildplan_generator/output/25-088 GENERATED BUILD PLAN.xlsx
@@ -714,7 +714,7 @@
         <v>2</v>
       </c>
       <c r="F9" s="9" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="G9" s="8" t="inlineStr">
         <is>
@@ -723,7 +723,7 @@
       </c>
       <c r="H9" s="8" t="inlineStr">
         <is>
-          <t>group_total:2h</t>
+          <t>group_total:3h</t>
         </is>
       </c>
       <c r="I9" s="8" t="n"/>
@@ -751,7 +751,7 @@
         <v>3</v>
       </c>
       <c r="F10" s="9" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="G10" s="8" t="inlineStr">
         <is>
@@ -760,7 +760,7 @@
       </c>
       <c r="H10" s="8" t="inlineStr">
         <is>
-          <t>group_total:2h</t>
+          <t>group_total:3h</t>
         </is>
       </c>
       <c r="I10" s="8" t="n"/>
@@ -805,7 +805,7 @@
         <v>2</v>
       </c>
       <c r="F12" s="9" t="n">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
@@ -814,7 +814,7 @@
       </c>
       <c r="H12" s="8" t="inlineStr">
         <is>
-          <t>group_total:3h</t>
+          <t>group_total:2h</t>
         </is>
       </c>
       <c r="I12" s="8" t="n"/>
@@ -842,7 +842,7 @@
         <v>1</v>
       </c>
       <c r="F13" s="9" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="G13" s="8" t="inlineStr">
         <is>
@@ -851,7 +851,7 @@
       </c>
       <c r="H13" s="8" t="inlineStr">
         <is>
-          <t>group_total:3h</t>
+          <t>group_total:2h</t>
         </is>
       </c>
       <c r="I13" s="8" t="n"/>
@@ -896,7 +896,7 @@
         <v>5</v>
       </c>
       <c r="F15" s="9" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="G15" s="8" t="inlineStr">
         <is>
@@ -949,17 +949,17 @@
       <c r="E17" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F17" s="9" t="n">
-        <v>1.1</v>
+      <c r="F17" s="10" t="n">
+        <v>1</v>
       </c>
       <c r="G17" s="8" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>none</t>
         </is>
       </c>
       <c r="H17" s="8" t="inlineStr">
         <is>
-          <t>group_total:1h</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="I17" s="8" t="n"/>
@@ -1037,7 +1037,7 @@
         <v>2</v>
       </c>
       <c r="F20" s="9" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="G20" s="8" t="inlineStr">
         <is>
@@ -1046,7 +1046,7 @@
       </c>
       <c r="H20" s="8" t="inlineStr">
         <is>
-          <t>group_total:4h</t>
+          <t>group_total:2h</t>
         </is>
       </c>
       <c r="I20" s="8" t="n"/>
@@ -1073,9 +1073,7 @@
       <c r="E21" s="8" t="n">
         <v>1</v>
       </c>
-      <c r="F21" s="9" t="n">
-        <v>0.1</v>
-      </c>
+      <c r="F21" s="8" t="n"/>
       <c r="G21" s="8" t="inlineStr">
         <is>
           <t>high</t>
@@ -1083,7 +1081,7 @@
       </c>
       <c r="H21" s="8" t="inlineStr">
         <is>
-          <t>group_total:4h</t>
+          <t>group_total:2h</t>
         </is>
       </c>
       <c r="I21" s="8" t="n"/>
@@ -1111,7 +1109,7 @@
         <v>1</v>
       </c>
       <c r="F22" s="9" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="G22" s="8" t="inlineStr">
         <is>
@@ -1120,7 +1118,7 @@
       </c>
       <c r="H22" s="8" t="inlineStr">
         <is>
-          <t>group_total:4h</t>
+          <t>group_total:2h</t>
         </is>
       </c>
       <c r="I22" s="8" t="n"/>
@@ -1148,7 +1146,7 @@
         <v>2</v>
       </c>
       <c r="F23" s="9" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="G23" s="8" t="inlineStr">
         <is>
@@ -1157,7 +1155,7 @@
       </c>
       <c r="H23" s="8" t="inlineStr">
         <is>
-          <t>group_total:4h</t>
+          <t>group_total:2h</t>
         </is>
       </c>
       <c r="I23" s="8" t="n"/>
@@ -1202,7 +1200,7 @@
         <v>2</v>
       </c>
       <c r="F25" s="9" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="G25" s="8" t="inlineStr">
         <is>
@@ -1211,7 +1209,7 @@
       </c>
       <c r="H25" s="8" t="inlineStr">
         <is>
-          <t>group_total:1h</t>
+          <t>group_total:5h</t>
         </is>
       </c>
       <c r="I25" s="8" t="n"/>
@@ -1239,7 +1237,7 @@
         <v>1</v>
       </c>
       <c r="F26" s="9" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="G26" s="8" t="inlineStr">
         <is>
@@ -1248,7 +1246,7 @@
       </c>
       <c r="H26" s="8" t="inlineStr">
         <is>
-          <t>group_total:1h</t>
+          <t>group_total:5h</t>
         </is>
       </c>
       <c r="I26" s="8" t="n"/>
@@ -1276,7 +1274,7 @@
         <v>1</v>
       </c>
       <c r="F27" s="9" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="G27" s="8" t="inlineStr">
         <is>
@@ -1285,7 +1283,7 @@
       </c>
       <c r="H27" s="8" t="inlineStr">
         <is>
-          <t>group_total:1h</t>
+          <t>group_total:5h</t>
         </is>
       </c>
       <c r="I27" s="8" t="n"/>
@@ -1313,7 +1311,7 @@
         <v>1</v>
       </c>
       <c r="F28" s="9" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="G28" s="8" t="inlineStr">
         <is>
@@ -1322,7 +1320,7 @@
       </c>
       <c r="H28" s="8" t="inlineStr">
         <is>
-          <t>group_total:1h</t>
+          <t>group_total:5h</t>
         </is>
       </c>
       <c r="I28" s="8" t="n"/>
@@ -1400,7 +1398,7 @@
         <v>1</v>
       </c>
       <c r="F31" s="9" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="G31" s="8" t="inlineStr">
         <is>
@@ -1507,7 +1505,7 @@
         <v>1</v>
       </c>
       <c r="F34" s="9" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="G34" s="8" t="inlineStr">
         <is>
@@ -1544,7 +1542,7 @@
         <v>3</v>
       </c>
       <c r="F35" s="9" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="G35" s="8" t="inlineStr">
         <is>
@@ -1635,7 +1633,7 @@
         <v>5</v>
       </c>
       <c r="F38" s="9" t="n">
-        <v>5.6</v>
+        <v>4.9</v>
       </c>
       <c r="G38" s="8" t="inlineStr">
         <is>
@@ -1644,7 +1642,7 @@
       </c>
       <c r="H38" s="8" t="inlineStr">
         <is>
-          <t>group_total:15h</t>
+          <t>group_total:13h</t>
         </is>
       </c>
       <c r="I38" s="8" t="n"/>
@@ -1672,7 +1670,7 @@
         <v>1</v>
       </c>
       <c r="F39" s="9" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="G39" s="8" t="inlineStr">
         <is>
@@ -1681,7 +1679,7 @@
       </c>
       <c r="H39" s="8" t="inlineStr">
         <is>
-          <t>group_total:15h</t>
+          <t>group_total:13h</t>
         </is>
       </c>
       <c r="I39" s="8" t="n"/>
@@ -1709,7 +1707,7 @@
         <v>3</v>
       </c>
       <c r="F40" s="9" t="n">
-        <v>5.5</v>
+        <v>4.9</v>
       </c>
       <c r="G40" s="8" t="inlineStr">
         <is>
@@ -1718,7 +1716,7 @@
       </c>
       <c r="H40" s="8" t="inlineStr">
         <is>
-          <t>group_total:15h</t>
+          <t>group_total:13h</t>
         </is>
       </c>
       <c r="I40" s="8" t="n"/>
@@ -1755,7 +1753,7 @@
       </c>
       <c r="H41" s="8" t="inlineStr">
         <is>
-          <t>group_total:15h</t>
+          <t>group_total:13h</t>
         </is>
       </c>
       <c r="I41" s="8" t="n"/>
@@ -1800,7 +1798,7 @@
         <v>1</v>
       </c>
       <c r="F43" s="9" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="G43" s="8" t="inlineStr">
         <is>
@@ -1809,7 +1807,7 @@
       </c>
       <c r="H43" s="8" t="inlineStr">
         <is>
-          <t>group_total:15h</t>
+          <t>group_total:13h</t>
         </is>
       </c>
       <c r="I43" s="8" t="n"/>
@@ -2240,7 +2238,7 @@
         </is>
       </c>
       <c r="F58" s="1" t="n">
-        <v>54.7</v>
+        <v>55.3</v>
       </c>
     </row>
   </sheetData>
@@ -3801,7 +3799,7 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -3810,7 +3808,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>group_total:2h</t>
+          <t>group_total:3h</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -3831,7 +3829,7 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1.3</v>
+        <v>2</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -3840,7 +3838,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>group_total:2h</t>
+          <t>group_total:3h</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -3861,7 +3859,7 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2.4</v>
+        <v>1.7</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -3870,7 +3868,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>group_total:3h</t>
+          <t>group_total:2h</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -3891,7 +3889,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3900,7 +3898,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>group_total:3h</t>
+          <t>group_total:2h</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -3921,7 +3919,7 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -3951,21 +3949,21 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>none</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>group_total:1h</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>model(MISC_PARTS)</t>
+          <t>nan</t>
         </is>
       </c>
     </row>
@@ -4011,7 +4009,7 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -4020,7 +4018,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>group_total:4h</t>
+          <t>group_total:2h</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -4041,7 +4039,7 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -4050,7 +4048,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>group_total:4h</t>
+          <t>group_total:2h</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -4071,7 +4069,7 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.9</v>
+        <v>0.6</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -4080,7 +4078,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>group_total:4h</t>
+          <t>group_total:2h</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -4101,7 +4099,7 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1.7</v>
+        <v>1.2</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -4110,7 +4108,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>group_total:4h</t>
+          <t>group_total:2h</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -4161,7 +4159,7 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4170,7 +4168,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>group_total:1h</t>
+          <t>group_total:5h</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -4191,7 +4189,7 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4200,7 +4198,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>group_total:1h</t>
+          <t>group_total:5h</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -4221,7 +4219,7 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0.3</v>
+        <v>1</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4230,7 +4228,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>group_total:1h</t>
+          <t>group_total:5h</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -4251,7 +4249,7 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>0.5</v>
+        <v>1.8</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4260,7 +4258,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>group_total:1h</t>
+          <t>group_total:5h</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -4311,7 +4309,7 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4401,7 +4399,7 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4431,7 +4429,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4491,7 +4489,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>5.6</v>
+        <v>4.9</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4500,7 +4498,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>group_total:15h</t>
+          <t>group_total:13h</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -4521,7 +4519,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4530,7 +4528,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>group_total:15h</t>
+          <t>group_total:13h</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -4551,7 +4549,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>5.5</v>
+        <v>4.9</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4560,7 +4558,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>group_total:15h</t>
+          <t>group_total:13h</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -4590,7 +4588,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>group_total:15h</t>
+          <t>group_total:13h</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -4611,7 +4609,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4620,7 +4618,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>group_total:15h</t>
+          <t>group_total:13h</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
